--- a/astro-site/public/dl/kit-plan-financiero/BONUS-08-simulador-escenarios.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/BONUS-08-simulador-escenarios.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Simulador" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comparativa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulador" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Simulador'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Comparativa'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,8 +22,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -136,45 +139,45 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="3" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -534,15 +537,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -550,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -557,6 +562,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -585,9 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -616,8 +620,25 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -626,15 +647,15 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,6 +672,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -776,6 +798,7 @@
         <v>18500</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -791,15 +814,15 @@
       </c>
       <c r="B14" s="12">
         <f>B6*B7*B8</f>
-        <v/>
+        <v>16000.0</v>
       </c>
       <c r="C14" s="12">
         <f>C6*C7*C8</f>
-        <v/>
+        <v>34320.0</v>
       </c>
       <c r="D14" s="12">
         <f>D6*D7*D8</f>
-        <v/>
+        <v>68850.0</v>
       </c>
     </row>
     <row r="15">
@@ -810,15 +833,15 @@
       </c>
       <c r="B15" s="12">
         <f>B14*B9</f>
-        <v/>
+        <v>6080.0</v>
       </c>
       <c r="C15" s="12">
         <f>C14*C9</f>
-        <v/>
+        <v>10982.4</v>
       </c>
       <c r="D15" s="12">
         <f>D14*D9</f>
-        <v/>
+        <v>19278.000000000004</v>
       </c>
     </row>
     <row r="16">
@@ -829,15 +852,15 @@
       </c>
       <c r="B16" s="12">
         <f>B14*B10</f>
-        <v/>
+        <v>5120.0</v>
       </c>
       <c r="C16" s="12">
         <f>C14*C10</f>
-        <v/>
+        <v>9609.6</v>
       </c>
       <c r="D16" s="12">
         <f>D14*D10</f>
-        <v/>
+        <v>17212.5</v>
       </c>
     </row>
     <row r="17">
@@ -848,15 +871,15 @@
       </c>
       <c r="B17" s="12">
         <f>B11</f>
-        <v/>
+        <v>19500.0</v>
       </c>
       <c r="C17" s="12">
         <f>C11</f>
-        <v/>
+        <v>19000.0</v>
       </c>
       <c r="D17" s="12">
         <f>D11</f>
-        <v/>
+        <v>18500.0</v>
       </c>
     </row>
     <row r="18">
@@ -867,15 +890,15 @@
       </c>
       <c r="B18" s="12">
         <f>B15+B16+B17</f>
-        <v/>
+        <v>30700.0</v>
       </c>
       <c r="C18" s="12">
         <f>C15+C16+C17</f>
-        <v/>
+        <v>39592.0</v>
       </c>
       <c r="D18" s="12">
         <f>D15+D16+D17</f>
-        <v/>
+        <v>54990.5</v>
       </c>
     </row>
     <row r="19">
@@ -886,15 +909,15 @@
       </c>
       <c r="B19" s="14">
         <f>B14-B18</f>
-        <v/>
+        <v>-14700.0</v>
       </c>
       <c r="C19" s="14">
         <f>C14-C18</f>
-        <v/>
+        <v>-5272.0</v>
       </c>
       <c r="D19" s="14">
         <f>D14-D18</f>
-        <v/>
+        <v>13859.5</v>
       </c>
     </row>
     <row r="20">
@@ -905,15 +928,15 @@
       </c>
       <c r="B20" s="15">
         <f>IF(B14=0,0,B19/B14)</f>
-        <v/>
+        <v>-0.91875</v>
       </c>
       <c r="C20" s="15">
         <f>IF(C14=0,0,C19/C14)</f>
-        <v/>
+        <v>-0.1536130536130536</v>
       </c>
       <c r="D20" s="15">
         <f>IF(D14=0,0,D19/D14)</f>
-        <v/>
+        <v>0.20129992737835875</v>
       </c>
     </row>
     <row r="21">
@@ -924,17 +947,19 @@
       </c>
       <c r="B21" s="14">
         <f>B19*12</f>
-        <v/>
+        <v>-176400.0</v>
       </c>
       <c r="C21" s="14">
         <f>C19*12</f>
-        <v/>
+        <v>-63264.0</v>
       </c>
       <c r="D21" s="14">
         <f>D19*12</f>
-        <v/>
-      </c>
-    </row>
+        <v>166314.0</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
@@ -948,7 +973,16 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -957,16 +991,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="30"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,6 +1010,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
@@ -1007,15 +1042,15 @@
       </c>
       <c r="C4" s="12">
         <f>Simulador!B14*12</f>
-        <v/>
+        <v>192000.0</v>
       </c>
       <c r="D4" s="12">
         <f>Simulador!C14*12</f>
-        <v/>
+        <v>411840.0</v>
       </c>
       <c r="E4" s="12">
         <f>Simulador!D14*12</f>
-        <v/>
+        <v>826200.0</v>
       </c>
     </row>
     <row r="5">
@@ -1026,15 +1061,15 @@
       </c>
       <c r="C5" s="12">
         <f>Simulador!B15*12</f>
-        <v/>
+        <v>72960.0</v>
       </c>
       <c r="D5" s="12">
         <f>Simulador!C15*12</f>
-        <v/>
+        <v>131788.8</v>
       </c>
       <c r="E5" s="12">
         <f>Simulador!D15*12</f>
-        <v/>
+        <v>231336.00000000006</v>
       </c>
     </row>
     <row r="6">
@@ -1045,15 +1080,15 @@
       </c>
       <c r="C6" s="12">
         <f>Simulador!B16*12</f>
-        <v/>
+        <v>61440.0</v>
       </c>
       <c r="D6" s="12">
         <f>Simulador!C16*12</f>
-        <v/>
+        <v>115315.20000000001</v>
       </c>
       <c r="E6" s="12">
         <f>Simulador!D16*12</f>
-        <v/>
+        <v>206550.0</v>
       </c>
     </row>
     <row r="7">
@@ -1064,15 +1099,15 @@
       </c>
       <c r="C7" s="12">
         <f>Simulador!B21</f>
-        <v/>
+        <v>-176400.0</v>
       </c>
       <c r="D7" s="12">
         <f>Simulador!C21</f>
-        <v/>
+        <v>-63264.0</v>
       </c>
       <c r="E7" s="12">
         <f>Simulador!D21</f>
-        <v/>
+        <v>166314.0</v>
       </c>
     </row>
     <row r="8">
@@ -1083,17 +1118,19 @@
       </c>
       <c r="C8" s="15">
         <f>Simulador!B20</f>
-        <v/>
+        <v>-0.91875</v>
       </c>
       <c r="D8" s="15">
         <f>Simulador!C20</f>
-        <v/>
+        <v>-0.1536130536130536</v>
       </c>
       <c r="E8" s="15">
         <f>Simulador!D20</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.20129992737835875</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -1106,6 +1143,15 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-plan-financiero/BONUS-08-simulador-escenarios.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/BONUS-08-simulador-escenarios.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +94,17 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +121,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,10 +187,43 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -247,6 +294,131 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>EBITDA anual por escenario</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Comparativa'!B7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Comparativa'!$C$3:$E$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Comparativa'!$C$7:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>€</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,11 +711,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -573,7 +745,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>▸ Cambia los valores de Ticket Medio, Ocupación y Food Cost en la zona de inputs.</t>
+          <t>▸ Cambia los valores de Ticket medio, Cubiertos / día y Food Cost en la zona de inputs.</t>
         </is>
       </c>
     </row>
@@ -622,13 +794,35 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA; en el 03 (tesorería) van CON IVA porque es caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -652,7 +846,7 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -672,7 +866,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>VALORES DE EJEMPLO — sustitúyelos por los tuyos</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -705,17 +905,17 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Ticket medio (€)</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="9" t="n">
+          <t>Ticket medio (€, sin IVA)</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>30</v>
+      <c r="D6" s="19" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -724,14 +924,14 @@
           <t>Cubiertos / día</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>85</v>
+      <c r="C7" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -740,30 +940,30 @@
           <t>Días apertura / mes</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="20" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Food Cost %</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0.28</v>
+          <t>% Coste variable (food + comisiones de delivery)</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -772,33 +972,39 @@
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Costes fijos mensuales (€)</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>19500</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>19000</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Costes fijos mensuales SIN personal y SIN cuota de préstamo (alquiler, suministros, seguros, marketing, gestoría, otros)</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Si copias los costes fijos del 02, RESTA antes las nóminas y la cuota: el personal ya entra arriba como % sobre ventas y el EBITDA se mide antes del servicio de deuda.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -809,20 +1015,20 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Facturación mensual</t>
+          <t>Facturación mensual (sin IVA)</t>
         </is>
       </c>
       <c r="B14" s="12">
         <f>B6*B7*B8</f>
-        <v>16000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="C14" s="12">
         <f>C6*C7*C8</f>
-        <v>34320.0</v>
+        <v>31460.0</v>
       </c>
       <c r="D14" s="12">
         <f>D6*D7*D8</f>
-        <v>68850.0</v>
+        <v>56700.0</v>
       </c>
     </row>
     <row r="15">
@@ -833,15 +1039,15 @@
       </c>
       <c r="B15" s="12">
         <f>B14*B9</f>
-        <v>6080.0</v>
+        <v>7200.0</v>
       </c>
       <c r="C15" s="12">
         <f>C14*C9</f>
-        <v>10982.4</v>
+        <v>11011.0</v>
       </c>
       <c r="D15" s="12">
         <f>D14*D9</f>
-        <v>19278.000000000004</v>
+        <v>17010.0</v>
       </c>
     </row>
     <row r="16">
@@ -852,15 +1058,15 @@
       </c>
       <c r="B16" s="12">
         <f>B14*B10</f>
-        <v>5120.0</v>
+        <v>5760.0</v>
       </c>
       <c r="C16" s="12">
         <f>C14*C10</f>
-        <v>9609.6</v>
+        <v>8808.800000000001</v>
       </c>
       <c r="D16" s="12">
         <f>D14*D10</f>
-        <v>17212.5</v>
+        <v>14175.0</v>
       </c>
     </row>
     <row r="17">
@@ -871,15 +1077,15 @@
       </c>
       <c r="B17" s="12">
         <f>B11</f>
-        <v>19500.0</v>
+        <v>6500.0</v>
       </c>
       <c r="C17" s="12">
         <f>C11</f>
-        <v>19000.0</v>
+        <v>6200.0</v>
       </c>
       <c r="D17" s="12">
         <f>D11</f>
-        <v>18500.0</v>
+        <v>5900.0</v>
       </c>
     </row>
     <row r="18">
@@ -890,15 +1096,15 @@
       </c>
       <c r="B18" s="12">
         <f>B15+B16+B17</f>
-        <v>30700.0</v>
+        <v>19460.0</v>
       </c>
       <c r="C18" s="12">
         <f>C15+C16+C17</f>
-        <v>39592.0</v>
+        <v>26019.800000000003</v>
       </c>
       <c r="D18" s="12">
         <f>D15+D16+D17</f>
-        <v>54990.5</v>
+        <v>37085.0</v>
       </c>
     </row>
     <row r="19">
@@ -909,15 +1115,15 @@
       </c>
       <c r="B19" s="14">
         <f>B14-B18</f>
-        <v>-14700.0</v>
+        <v>-1460.0</v>
       </c>
       <c r="C19" s="14">
         <f>C14-C18</f>
-        <v>-5272.0</v>
+        <v>5440.199999999997</v>
       </c>
       <c r="D19" s="14">
         <f>D14-D18</f>
-        <v>13859.5</v>
+        <v>19615.0</v>
       </c>
     </row>
     <row r="20">
@@ -927,16 +1133,16 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>IF(B14=0,0,B19/B14)</f>
-        <v>-0.91875</v>
+        <f>IF(B14=0,"",B19/B14)</f>
+        <v>-0.0811111111111111</v>
       </c>
       <c r="C20" s="15">
-        <f>IF(C14=0,0,C19/C14)</f>
-        <v>-0.1536130536130536</v>
+        <f>IF(C14=0,"",C19/C14)</f>
+        <v>0.17292434837889373</v>
       </c>
       <c r="D20" s="15">
-        <f>IF(D14=0,0,D19/D14)</f>
-        <v>0.20129992737835875</v>
+        <f>IF(D14=0,"",D19/D14)</f>
+        <v>0.3459435626102293</v>
       </c>
     </row>
     <row r="21">
@@ -947,18 +1153,24 @@
       </c>
       <c r="B21" s="14">
         <f>B19*12</f>
-        <v>-176400.0</v>
+        <v>-17520.0</v>
       </c>
       <c r="C21" s="14">
         <f>C19*12</f>
-        <v>-63264.0</v>
+        <v>65282.399999999965</v>
       </c>
       <c r="D21" s="14">
         <f>D19*12</f>
-        <v>166314.0</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>235380.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Base común con el 02: mismo ticket (22 €), mismos cubiertos/día (55), mismos días (26), mismo % de coste variable (35 %) y los mismos costes fijos sin personal (6.200 €). El EBITDA base coincide: ~17 % sobre ventas en los dos libros.</t>
+        </is>
+      </c>
+    </row>
     <row r="23"/>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -968,11 +1180,26 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B19:D19">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>=B19&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B6 B7 B8 B11 C6 C7 C8 C11 D6 D7 D8 D11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9 B10 C9 C10 D9 D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1037,20 +1264,20 @@
     <row r="4">
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Facturación anual</t>
+          <t>Facturación anual (sin IVA)</t>
         </is>
       </c>
       <c r="C4" s="12">
         <f>Simulador!B14*12</f>
-        <v>192000.0</v>
+        <v>216000.0</v>
       </c>
       <c r="D4" s="12">
         <f>Simulador!C14*12</f>
-        <v>411840.0</v>
+        <v>377520.0</v>
       </c>
       <c r="E4" s="12">
         <f>Simulador!D14*12</f>
-        <v>826200.0</v>
+        <v>680400.0</v>
       </c>
     </row>
     <row r="5">
@@ -1061,15 +1288,15 @@
       </c>
       <c r="C5" s="12">
         <f>Simulador!B15*12</f>
-        <v>72960.0</v>
+        <v>86400.0</v>
       </c>
       <c r="D5" s="12">
         <f>Simulador!C15*12</f>
-        <v>131788.8</v>
+        <v>132132.0</v>
       </c>
       <c r="E5" s="12">
         <f>Simulador!D15*12</f>
-        <v>231336.00000000006</v>
+        <v>204120.0</v>
       </c>
     </row>
     <row r="6">
@@ -1080,15 +1307,15 @@
       </c>
       <c r="C6" s="12">
         <f>Simulador!B16*12</f>
-        <v>61440.0</v>
+        <v>69120.0</v>
       </c>
       <c r="D6" s="12">
         <f>Simulador!C16*12</f>
-        <v>115315.20000000001</v>
+        <v>105705.6</v>
       </c>
       <c r="E6" s="12">
         <f>Simulador!D16*12</f>
-        <v>206550.0</v>
+        <v>170100.0</v>
       </c>
     </row>
     <row r="7">
@@ -1099,15 +1326,15 @@
       </c>
       <c r="C7" s="12">
         <f>Simulador!B21</f>
-        <v>-176400.0</v>
+        <v>-17520.0</v>
       </c>
       <c r="D7" s="12">
         <f>Simulador!C21</f>
-        <v>-63264.0</v>
+        <v>65282.399999999965</v>
       </c>
       <c r="E7" s="12">
         <f>Simulador!D21</f>
-        <v>166314.0</v>
+        <v>235380.0</v>
       </c>
     </row>
     <row r="8">
@@ -1118,15 +1345,15 @@
       </c>
       <c r="C8" s="15">
         <f>Simulador!B20</f>
-        <v>-0.91875</v>
+        <v>-0.0811111111111111</v>
       </c>
       <c r="D8" s="15">
         <f>Simulador!C20</f>
-        <v>-0.1536130536130536</v>
+        <v>0.17292434837889373</v>
       </c>
       <c r="E8" s="15">
         <f>Simulador!D20</f>
-        <v>0.20129992737835875</v>
+        <v>0.3459435626102293</v>
       </c>
     </row>
     <row r="9"/>
@@ -1139,10 +1366,16 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
+  <conditionalFormatting sqref="C7:E7">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>=C7&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1153,5 +1386,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>